--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/147.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/147.xlsx
@@ -426,13 +426,13 @@
         <v>-0.8535674694735157</v>
       </c>
       <c r="E2">
-        <v>-17.16329442912089</v>
+        <v>-19.55825036366149</v>
       </c>
       <c r="F2">
-        <v>-4.116465666500383</v>
+        <v>-3.593899727818321</v>
       </c>
       <c r="G2">
-        <v>-8.821585364799953</v>
+        <v>-7.635857200635809</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.1425821889103776</v>
       </c>
       <c r="E3">
-        <v>-18.42839609874773</v>
+        <v>-18.91257148269983</v>
       </c>
       <c r="F3">
-        <v>-4.176673414287644</v>
+        <v>-3.781183246407486</v>
       </c>
       <c r="G3">
-        <v>-9.12280197178162</v>
+        <v>-9.786433930583922</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.6045283798358679</v>
       </c>
       <c r="E4">
-        <v>-19.89801271150898</v>
+        <v>-20.42183488539823</v>
       </c>
       <c r="F4">
-        <v>-4.247636900799613</v>
+        <v>-3.659512663894978</v>
       </c>
       <c r="G4">
-        <v>-9.203840816037438</v>
+        <v>-9.246404500035849</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>1.315981067614674</v>
       </c>
       <c r="E5">
-        <v>-19.35245386238291</v>
+        <v>-19.96584925214388</v>
       </c>
       <c r="F5">
-        <v>-4.332224217449149</v>
+        <v>-3.540875670063493</v>
       </c>
       <c r="G5">
-        <v>-8.362879485424076</v>
+        <v>-9.224223844922731</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.020565720414095</v>
       </c>
       <c r="E6">
-        <v>-19.98928863360758</v>
+        <v>-19.32800010274148</v>
       </c>
       <c r="F6">
-        <v>-4.340842745040971</v>
+        <v>-4.05981808961103</v>
       </c>
       <c r="G6">
-        <v>-8.190575521741629</v>
+        <v>-10.95283181934426</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.705080492693318</v>
       </c>
       <c r="E7">
-        <v>-20.31573726787252</v>
+        <v>-21.26418992098701</v>
       </c>
       <c r="F7">
-        <v>-4.39788070543848</v>
+        <v>-3.666256875535876</v>
       </c>
       <c r="G7">
-        <v>-8.268618322284407</v>
+        <v>-8.499379899099305</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.38456841063564</v>
       </c>
       <c r="E8">
-        <v>-21.63263562319909</v>
+        <v>-20.23920152866888</v>
       </c>
       <c r="F8">
-        <v>-4.567161447033887</v>
+        <v>-3.494500801594637</v>
       </c>
       <c r="G8">
-        <v>-8.808611336831548</v>
+        <v>-8.316141203500646</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.057458799600297</v>
       </c>
       <c r="E9">
-        <v>-20.93754203386574</v>
+        <v>-21.66401794807225</v>
       </c>
       <c r="F9">
-        <v>-4.438988168032584</v>
+        <v>-3.916944852302617</v>
       </c>
       <c r="G9">
-        <v>-8.3082554840261</v>
+        <v>-9.700104834556347</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.719871783771136</v>
       </c>
       <c r="E10">
-        <v>-21.81809021923522</v>
+        <v>-22.18886808556124</v>
       </c>
       <c r="F10">
-        <v>-4.443550824774965</v>
+        <v>-4.061163447786195</v>
       </c>
       <c r="G10">
-        <v>-8.197971280476359</v>
+        <v>-7.550008133711428</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.366209741536973</v>
       </c>
       <c r="E11">
-        <v>-22.71140870130633</v>
+        <v>-22.32999344953628</v>
       </c>
       <c r="F11">
-        <v>-4.480474136340479</v>
+        <v>-2.669573729536876</v>
       </c>
       <c r="G11">
-        <v>-8.199646416519231</v>
+        <v>-9.017649113817749</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.982139327158124</v>
       </c>
       <c r="E12">
-        <v>-22.77631531925826</v>
+        <v>-22.76808708198633</v>
       </c>
       <c r="F12">
-        <v>-4.428317157574353</v>
+        <v>-3.554684793793167</v>
       </c>
       <c r="G12">
-        <v>-7.558843979755743</v>
+        <v>-7.364604341330085</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.54307038387222</v>
       </c>
       <c r="E13">
-        <v>-22.97178689979935</v>
+        <v>-25.54527339361834</v>
       </c>
       <c r="F13">
-        <v>-4.453569348396035</v>
+        <v>-3.76735036708908</v>
       </c>
       <c r="G13">
-        <v>-7.040356269031707</v>
+        <v>-8.5046734614166</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>7.028636109390273</v>
       </c>
       <c r="E14">
-        <v>-24.39184389302066</v>
+        <v>-24.25958528115263</v>
       </c>
       <c r="F14">
-        <v>-4.559756038173292</v>
+        <v>-3.355514770455672</v>
       </c>
       <c r="G14">
-        <v>-6.631785291302554</v>
+        <v>-8.09013688062568</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>7.41359443851432</v>
       </c>
       <c r="E15">
-        <v>-25.50065886769477</v>
+        <v>-26.90024715840141</v>
       </c>
       <c r="F15">
-        <v>-4.336011650145923</v>
+        <v>-3.314829365488032</v>
       </c>
       <c r="G15">
-        <v>-6.798285868654659</v>
+        <v>-5.673170482769032</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.677656272674206</v>
       </c>
       <c r="E16">
-        <v>-26.22309538308644</v>
+        <v>-25.52849539741992</v>
       </c>
       <c r="F16">
-        <v>-3.997384443159618</v>
+        <v>-3.042903892395248</v>
       </c>
       <c r="G16">
-        <v>-6.851284392192851</v>
+        <v>-7.92606293315386</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.8107840663395</v>
       </c>
       <c r="E17">
-        <v>-25.93190091897121</v>
+        <v>-26.53628464545692</v>
       </c>
       <c r="F17">
-        <v>-3.463264577971467</v>
+        <v>-2.756670428209426</v>
       </c>
       <c r="G17">
-        <v>-6.091888282576051</v>
+        <v>-6.437926365613912</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.804156632451594</v>
       </c>
       <c r="E18">
-        <v>-27.95044556552024</v>
+        <v>-27.63914920528496</v>
       </c>
       <c r="F18">
-        <v>-3.506234478722128</v>
+        <v>-2.464833020641822</v>
       </c>
       <c r="G18">
-        <v>-6.127311119846254</v>
+        <v>-6.6271273537288</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.658246611727395</v>
       </c>
       <c r="E19">
-        <v>-27.41844949604714</v>
+        <v>-28.37856296973138</v>
       </c>
       <c r="F19">
-        <v>-3.270812635127266</v>
+        <v>-1.992039791470191</v>
       </c>
       <c r="G19">
-        <v>-5.168544026217925</v>
+        <v>-6.404585861487912</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.379885786401002</v>
       </c>
       <c r="E20">
-        <v>-28.21362236095001</v>
+        <v>-29.20695671995452</v>
       </c>
       <c r="F20">
-        <v>-3.217100457152179</v>
+        <v>-1.534694029797757</v>
       </c>
       <c r="G20">
-        <v>-5.284962670651935</v>
+        <v>-5.77674421051067</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.975648104744577</v>
       </c>
       <c r="E21">
-        <v>-29.82682782754647</v>
+        <v>-29.33142635652935</v>
       </c>
       <c r="F21">
-        <v>-2.887920847804428</v>
+        <v>-1.482220309848544</v>
       </c>
       <c r="G21">
-        <v>-5.647947436305325</v>
+        <v>-5.428696626330472</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.460678812293096</v>
       </c>
       <c r="E22">
-        <v>-29.33432910836827</v>
+        <v>-30.02538782736079</v>
       </c>
       <c r="F22">
-        <v>-3.05763394111475</v>
+        <v>-0.9760971978335321</v>
       </c>
       <c r="G22">
-        <v>-4.458686920050779</v>
+        <v>-5.198901728813041</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.851212634981297</v>
       </c>
       <c r="E23">
-        <v>-30.31909106607626</v>
+        <v>-30.05023330000387</v>
       </c>
       <c r="F23">
-        <v>-2.368508859452964</v>
+        <v>-0.2431058378729463</v>
       </c>
       <c r="G23">
-        <v>-5.278281989753686</v>
+        <v>-5.693659449111581</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.160017668251368</v>
       </c>
       <c r="E24">
-        <v>-30.53078364051283</v>
+        <v>-31.56762078507203</v>
       </c>
       <c r="F24">
-        <v>-2.204092470576829</v>
+        <v>-0.9775850895410875</v>
       </c>
       <c r="G24">
-        <v>-5.238691175649542</v>
+        <v>-5.019390707491601</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.40718294982763</v>
       </c>
       <c r="E25">
-        <v>-32.14033010011109</v>
+        <v>-33.93482396665662</v>
       </c>
       <c r="F25">
-        <v>-1.990814003091641</v>
+        <v>-0.2272521498064397</v>
       </c>
       <c r="G25">
-        <v>-4.156106368306932</v>
+        <v>-5.755907636886498</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.61010926420423</v>
       </c>
       <c r="E26">
-        <v>-30.54973983270894</v>
+        <v>-30.7794964899621</v>
       </c>
       <c r="F26">
-        <v>-2.282759894514453</v>
+        <v>-0.9774045470667273</v>
       </c>
       <c r="G26">
-        <v>-4.932528613632203</v>
+        <v>-4.45100314385413</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.784332189034059</v>
       </c>
       <c r="E27">
-        <v>-31.10530660939196</v>
+        <v>-30.14138242483026</v>
       </c>
       <c r="F27">
-        <v>-2.343406328840291</v>
+        <v>-0.7771568118537751</v>
       </c>
       <c r="G27">
-        <v>-5.381256508752717</v>
+        <v>-5.847523674140288</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.959212847395431</v>
       </c>
       <c r="E28">
-        <v>-31.35156276169207</v>
+        <v>-31.02611039170882</v>
       </c>
       <c r="F28">
-        <v>-2.183088570873314</v>
+        <v>-0.9906799619028985</v>
       </c>
       <c r="G28">
-        <v>-5.456919027052759</v>
+        <v>-4.004235091692866</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.159954149109736</v>
       </c>
       <c r="E29">
-        <v>-30.70376229065782</v>
+        <v>-32.3528785561351</v>
       </c>
       <c r="F29">
-        <v>-2.114990008362375</v>
+        <v>-1.637862967953144</v>
       </c>
       <c r="G29">
-        <v>-5.43311289407986</v>
+        <v>-6.020691690208485</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.4150386356822703</v>
       </c>
       <c r="E30">
-        <v>-30.38671703266981</v>
+        <v>-32.45425750374482</v>
       </c>
       <c r="F30">
-        <v>-1.985243317534083</v>
+        <v>-0.7024803268230587</v>
       </c>
       <c r="G30">
-        <v>-4.997438480020693</v>
+        <v>-6.97734334523722</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2370857589660912</v>
       </c>
       <c r="E31">
-        <v>-30.66913531415817</v>
+        <v>-32.7219854155523</v>
       </c>
       <c r="F31">
-        <v>-1.702517761950959</v>
+        <v>-1.092246981524819</v>
       </c>
       <c r="G31">
-        <v>-5.941973538375695</v>
+        <v>-7.522173066817236</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7683119530026877</v>
       </c>
       <c r="E32">
-        <v>-29.87943963856758</v>
+        <v>-30.39914769382086</v>
       </c>
       <c r="F32">
-        <v>-2.440713179549679</v>
+        <v>-0.860953859251507</v>
       </c>
       <c r="G32">
-        <v>-6.764607688883653</v>
+        <v>-6.201808326116473</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.148438412348956</v>
       </c>
       <c r="E33">
-        <v>-30.65757638425359</v>
+        <v>-30.77458762413779</v>
       </c>
       <c r="F33">
-        <v>-2.110896920423922</v>
+        <v>-0.9577095803023223</v>
       </c>
       <c r="G33">
-        <v>-5.71492308311032</v>
+        <v>-6.843547647267575</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.349048366324474</v>
       </c>
       <c r="E34">
-        <v>-30.15642827972074</v>
+        <v>-31.26513683525568</v>
       </c>
       <c r="F34">
-        <v>-2.276768735036346</v>
+        <v>-1.176744026937175</v>
       </c>
       <c r="G34">
-        <v>-5.593806774556084</v>
+        <v>-6.337583730318602</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.360783958802038</v>
       </c>
       <c r="E35">
-        <v>-29.03824842079877</v>
+        <v>-30.27875141961594</v>
       </c>
       <c r="F35">
-        <v>-2.041879016629071</v>
+        <v>-1.006276297758146</v>
       </c>
       <c r="G35">
-        <v>-5.920577482555386</v>
+        <v>-7.714621700106148</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.173527169339316</v>
       </c>
       <c r="E36">
-        <v>-28.0937083692269</v>
+        <v>-29.73053888472137</v>
       </c>
       <c r="F36">
-        <v>-2.260550794609288</v>
+        <v>-0.7282543487438781</v>
       </c>
       <c r="G36">
-        <v>-6.054293727432088</v>
+        <v>-5.456286712854759</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.7904774422983638</v>
       </c>
       <c r="E37">
-        <v>-28.07681263270428</v>
+        <v>-31.84919903463197</v>
       </c>
       <c r="F37">
-        <v>-2.141067309966001</v>
+        <v>-1.053918130959353</v>
       </c>
       <c r="G37">
-        <v>-6.401937425056495</v>
+        <v>-5.948194053443986</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2350170681211226</v>
       </c>
       <c r="E38">
-        <v>-28.11231134045041</v>
+        <v>-29.48114676417095</v>
       </c>
       <c r="F38">
-        <v>-2.046095633628928</v>
+        <v>-0.6278275973810741</v>
       </c>
       <c r="G38">
-        <v>-6.324758676899465</v>
+        <v>-5.755798388883702</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4739582098649791</v>
       </c>
       <c r="E39">
-        <v>-27.60019527187098</v>
+        <v>-28.34457677230382</v>
       </c>
       <c r="F39">
-        <v>-2.343543319401977</v>
+        <v>-0.5982851472344666</v>
       </c>
       <c r="G39">
-        <v>-6.105703189111431</v>
+        <v>-6.048775048018123</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.303790813379552</v>
       </c>
       <c r="E40">
-        <v>-26.38649631070521</v>
+        <v>-27.97995763062822</v>
       </c>
       <c r="F40">
-        <v>-2.105644559755367</v>
+        <v>-1.313359250320728</v>
       </c>
       <c r="G40">
-        <v>-5.269012462243727</v>
+        <v>-6.325718735105855</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.213226935042422</v>
       </c>
       <c r="E41">
-        <v>-26.11217041226855</v>
+        <v>-27.38999709385694</v>
       </c>
       <c r="F41">
-        <v>-2.14130724141219</v>
+        <v>-0.9962807378728501</v>
       </c>
       <c r="G41">
-        <v>-5.856001981266362</v>
+        <v>-5.238949398201605</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.170314030779725</v>
       </c>
       <c r="E42">
-        <v>-26.12543431263702</v>
+        <v>-27.97521631834219</v>
       </c>
       <c r="F42">
-        <v>-2.181758257904344</v>
+        <v>-1.023149100581238</v>
       </c>
       <c r="G42">
-        <v>-5.125169258562393</v>
+        <v>-4.801930902653495</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.136308608757367</v>
       </c>
       <c r="E43">
-        <v>-25.78369302164818</v>
+        <v>-26.28002282983686</v>
       </c>
       <c r="F43">
-        <v>-2.079364543794564</v>
+        <v>-1.343706223072379</v>
       </c>
       <c r="G43">
-        <v>-5.515085312177754</v>
+        <v>-5.955523601267932</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.075014990806952</v>
       </c>
       <c r="E44">
-        <v>-25.18069047973481</v>
+        <v>-26.27770877961894</v>
       </c>
       <c r="F44">
-        <v>-2.369724353743064</v>
+        <v>-1.493136794723668</v>
       </c>
       <c r="G44">
-        <v>-5.360320618762366</v>
+        <v>-5.907471032765411</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.960117930042863</v>
       </c>
       <c r="E45">
-        <v>-24.70989673647538</v>
+        <v>-26.12992203037862</v>
       </c>
       <c r="F45">
-        <v>-2.497321955644105</v>
+        <v>-1.65050806783497</v>
       </c>
       <c r="G45">
-        <v>-5.975310731956156</v>
+        <v>-5.980312966265995</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.762373626936224</v>
       </c>
       <c r="E46">
-        <v>-23.80151202138075</v>
+        <v>-23.60916055943094</v>
       </c>
       <c r="F46">
-        <v>-2.514650865770843</v>
+        <v>-1.329540765511731</v>
       </c>
       <c r="G46">
-        <v>-5.750369094199296</v>
+        <v>-6.100883034806252</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>7.463476044621283</v>
       </c>
       <c r="E47">
-        <v>-23.33137490685243</v>
+        <v>-25.12208296912754</v>
       </c>
       <c r="F47">
-        <v>-2.441745755806546</v>
+        <v>-1.829411406572587</v>
       </c>
       <c r="G47">
-        <v>-5.361558762794053</v>
+        <v>-5.54758162719124</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>8.054511704704845</v>
       </c>
       <c r="E48">
-        <v>-22.5397704794676</v>
+        <v>-22.45400118176233</v>
       </c>
       <c r="F48">
-        <v>-2.228209144257141</v>
+        <v>-0.5931119718616836</v>
       </c>
       <c r="G48">
-        <v>-5.603079612611582</v>
+        <v>-5.542344344148113</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>8.523414273762853</v>
       </c>
       <c r="E49">
-        <v>-21.7862595754353</v>
+        <v>-22.21118440547104</v>
       </c>
       <c r="F49">
-        <v>-2.56260864830218</v>
+        <v>-1.114851216055886</v>
       </c>
       <c r="G49">
-        <v>-5.33527303121224</v>
+        <v>-6.034082846914838</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>8.871386871051337</v>
       </c>
       <c r="E50">
-        <v>-22.29421397640168</v>
+        <v>-21.67994911963123</v>
       </c>
       <c r="F50">
-        <v>-2.148752242920671</v>
+        <v>-1.736679090399946</v>
       </c>
       <c r="G50">
-        <v>-5.195015148349937</v>
+        <v>-6.85973621495461</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>9.101917694611876</v>
       </c>
       <c r="E51">
-        <v>-20.28367114342421</v>
+        <v>-22.24021192386021</v>
       </c>
       <c r="F51">
-        <v>-2.000579133766241</v>
+        <v>-1.511251222984464</v>
       </c>
       <c r="G51">
-        <v>-6.164511720071044</v>
+        <v>-6.755417614466636</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>9.212853586830818</v>
       </c>
       <c r="E52">
-        <v>-21.07639410388893</v>
+        <v>-21.54096119538781</v>
       </c>
       <c r="F52">
-        <v>-2.343015945332135</v>
+        <v>-0.9847671958676053</v>
       </c>
       <c r="G52">
-        <v>-6.52196787467385</v>
+        <v>-6.110980198701029</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>9.216716968054817</v>
       </c>
       <c r="E53">
-        <v>-21.00342680220333</v>
+        <v>-20.86993191693122</v>
       </c>
       <c r="F53">
-        <v>-2.426131207333271</v>
+        <v>-1.379705442236233</v>
       </c>
       <c r="G53">
-        <v>-6.596564397310248</v>
+        <v>-5.017407690713577</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>9.122616974759291</v>
       </c>
       <c r="E54">
-        <v>-19.54543025374577</v>
+        <v>-20.73884617983119</v>
       </c>
       <c r="F54">
-        <v>-2.849289509409114</v>
+        <v>-1.213897767713385</v>
       </c>
       <c r="G54">
-        <v>-6.151226500821949</v>
+        <v>-5.900469228949852</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>8.934655388406608</v>
       </c>
       <c r="E55">
-        <v>-19.8302486264582</v>
+        <v>-21.27979051394344</v>
       </c>
       <c r="F55">
-        <v>-2.250221864628792</v>
+        <v>-1.950028824651329</v>
       </c>
       <c r="G55">
-        <v>-6.374721430178147</v>
+        <v>-5.544055896191916</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>8.671700982196556</v>
       </c>
       <c r="E56">
-        <v>-18.93645465461628</v>
+        <v>-20.7437550456555</v>
       </c>
       <c r="F56">
-        <v>-2.525050270664576</v>
+        <v>-1.400835246560026</v>
       </c>
       <c r="G56">
-        <v>-6.263573174242655</v>
+        <v>-6.068972686353217</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>8.343547796914319</v>
       </c>
       <c r="E57">
-        <v>-18.96194090633145</v>
+        <v>-17.84982920257975</v>
       </c>
       <c r="F57">
-        <v>-2.198768051289122</v>
+        <v>-1.435843065820815</v>
       </c>
       <c r="G57">
-        <v>-6.469313647871742</v>
+        <v>-6.637340386717451</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>7.958559697968173</v>
       </c>
       <c r="E58">
-        <v>-18.27979422418603</v>
+        <v>-18.90262242530498</v>
       </c>
       <c r="F58">
-        <v>-2.560302772489301</v>
+        <v>-1.74452952062278</v>
       </c>
       <c r="G58">
-        <v>-7.658891976498057</v>
+        <v>-6.661017408414319</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>7.537666633969938</v>
       </c>
       <c r="E59">
-        <v>-18.44280117456613</v>
+        <v>-18.35292002246189</v>
       </c>
       <c r="F59">
-        <v>-2.547214234951151</v>
+        <v>-1.246487268041298</v>
       </c>
       <c r="G59">
-        <v>-7.237787273357223</v>
+        <v>-6.669042170801512</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>7.088819363686306</v>
       </c>
       <c r="E60">
-        <v>-17.69306248938222</v>
+        <v>-18.75705009985441</v>
       </c>
       <c r="F60">
-        <v>-2.714866135012529</v>
+        <v>-1.920621781360492</v>
       </c>
       <c r="G60">
-        <v>-6.452992658363135</v>
+        <v>-6.73209482114247</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>6.623915902063055</v>
       </c>
       <c r="E61">
-        <v>-17.31619382551587</v>
+        <v>-18.62355521458229</v>
       </c>
       <c r="F61">
-        <v>-2.58997667022689</v>
+        <v>-1.51173900440642</v>
       </c>
       <c r="G61">
-        <v>-7.482476315255835</v>
+        <v>-7.687882423785456</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>6.160331781523674</v>
       </c>
       <c r="E62">
-        <v>-17.44677237352705</v>
+        <v>-16.26633505394762</v>
       </c>
       <c r="F62">
-        <v>-2.741523864834163</v>
+        <v>-1.961056960793492</v>
       </c>
       <c r="G62">
-        <v>-6.983395022483007</v>
+        <v>-8.22204556763794</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>5.701163741972716</v>
       </c>
       <c r="E63">
-        <v>-17.11019354290695</v>
+        <v>-17.46929247476719</v>
       </c>
       <c r="F63">
-        <v>-2.848939510401802</v>
+        <v>-2.187317065667537</v>
       </c>
       <c r="G63">
-        <v>-7.418308011068142</v>
+        <v>-7.304431865608292</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>5.258377013327535</v>
       </c>
       <c r="E64">
-        <v>-16.50460071386119</v>
+        <v>-16.88537292232215</v>
       </c>
       <c r="F64">
-        <v>-2.942608588623425</v>
+        <v>-1.911625539907838</v>
       </c>
       <c r="G64">
-        <v>-7.298946291649719</v>
+        <v>-8.060560466777831</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>4.841890127677999</v>
       </c>
       <c r="E65">
-        <v>-17.59870267648439</v>
+        <v>-18.3234079573539</v>
       </c>
       <c r="F65">
-        <v>-3.107162759914204</v>
+        <v>-1.543084503737755</v>
       </c>
       <c r="G65">
-        <v>-7.85579329353729</v>
+        <v>-8.155788309214966</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>4.449353564475942</v>
       </c>
       <c r="E66">
-        <v>-17.24987432367354</v>
+        <v>-18.66490471074633</v>
       </c>
       <c r="F66">
-        <v>-3.055066753825823</v>
+        <v>-2.252005909342534</v>
       </c>
       <c r="G66">
-        <v>-8.307709244012122</v>
+        <v>-6.911023186449</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>4.091841821802494</v>
       </c>
       <c r="E67">
-        <v>-16.78211465799925</v>
+        <v>-17.18491789250752</v>
       </c>
       <c r="F67">
-        <v>-2.801249374170174</v>
+        <v>-2.870279155759391</v>
       </c>
       <c r="G67">
-        <v>-7.843103972485263</v>
+        <v>-8.634595821105297</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>3.773133365237656</v>
       </c>
       <c r="E68">
-        <v>-15.86083737740478</v>
+        <v>-17.87745289402654</v>
       </c>
       <c r="F68">
-        <v>-3.25062117655837</v>
+        <v>-2.637328685245572</v>
       </c>
       <c r="G68">
-        <v>-7.575320564904696</v>
+        <v>-8.547773453792372</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>3.48910463513562</v>
       </c>
       <c r="E69">
-        <v>-16.70113648579409</v>
+        <v>-17.45357414148657</v>
       </c>
       <c r="F69">
-        <v>-2.894023658549574</v>
+        <v>-2.423107912740697</v>
       </c>
       <c r="G69">
-        <v>-7.812888623348336</v>
+        <v>-8.321173232720337</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>3.249481007116612</v>
       </c>
       <c r="E70">
-        <v>-16.75670991881622</v>
+        <v>-16.00125177096062</v>
       </c>
       <c r="F70">
-        <v>-3.377840272745621</v>
+        <v>-2.809363491427928</v>
       </c>
       <c r="G70">
-        <v>-8.275044091176133</v>
+        <v>-8.308560054215715</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>3.053015472724973</v>
       </c>
       <c r="E71">
-        <v>-16.83868888377707</v>
+        <v>-16.62270331598124</v>
       </c>
       <c r="F71">
-        <v>-3.234703348402288</v>
+        <v>-2.96672447045078</v>
       </c>
       <c r="G71">
-        <v>-7.923143031988223</v>
+        <v>-6.699903076318598</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>2.895596660226752</v>
       </c>
       <c r="E72">
-        <v>-16.31193225873085</v>
+        <v>-16.13825622358868</v>
       </c>
       <c r="F72">
-        <v>-3.544956088354623</v>
+        <v>-2.360366235488732</v>
       </c>
       <c r="G72">
-        <v>-7.67078014552958</v>
+        <v>-8.650406986600856</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.783205220982995</v>
       </c>
       <c r="E73">
-        <v>-16.86072896677241</v>
+        <v>-17.48333980113899</v>
       </c>
       <c r="F73">
-        <v>-3.558959216058939</v>
+        <v>-3.476234337565959</v>
       </c>
       <c r="G73">
-        <v>-7.941198747359408</v>
+        <v>-7.239422682853624</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.710628835720699</v>
       </c>
       <c r="E74">
-        <v>-17.2598867797045</v>
+        <v>-15.97929320049743</v>
       </c>
       <c r="F74">
-        <v>-3.678096660959702</v>
+        <v>-2.83152508015563</v>
       </c>
       <c r="G74">
-        <v>-6.938106759505778</v>
+        <v>-7.22199266058936</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.674973391260401</v>
       </c>
       <c r="E75">
-        <v>-17.11902406722191</v>
+        <v>-17.94662986296771</v>
       </c>
       <c r="F75">
-        <v>-3.617164367716127</v>
+        <v>-3.598555823209713</v>
       </c>
       <c r="G75">
-        <v>-6.808525386007624</v>
+        <v>-6.850569314356369</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.676774872036023</v>
       </c>
       <c r="E76">
-        <v>-17.17603302650447</v>
+        <v>-16.37580185613503</v>
       </c>
       <c r="F76">
-        <v>-3.753873029748691</v>
+        <v>-3.130149459423849</v>
       </c>
       <c r="G76">
-        <v>-6.940275166834001</v>
+        <v>-7.414752485158965</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.706978168720065</v>
       </c>
       <c r="E77">
-        <v>-16.98015388330269</v>
+        <v>-19.76317286945658</v>
       </c>
       <c r="F77">
-        <v>-4.00009258027502</v>
+        <v>-2.564353892220995</v>
       </c>
       <c r="G77">
-        <v>-6.696129054403829</v>
+        <v>-6.251095728105143</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.760924413783306</v>
       </c>
       <c r="E78">
-        <v>-17.82363198044538</v>
+        <v>-17.99440073527463</v>
       </c>
       <c r="F78">
-        <v>-3.648581133813657</v>
+        <v>-3.10046526759781</v>
       </c>
       <c r="G78">
-        <v>-6.415715915590941</v>
+        <v>-6.931290346240418</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.831772237991254</v>
       </c>
       <c r="E79">
-        <v>-19.38002774061561</v>
+        <v>-18.81913095002556</v>
       </c>
       <c r="F79">
-        <v>-3.960397783357487</v>
+        <v>-3.504712537337391</v>
       </c>
       <c r="G79">
-        <v>-6.791492629208075</v>
+        <v>-5.797266282308613</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.905320692992579</v>
       </c>
       <c r="E80">
-        <v>-18.89655879860871</v>
+        <v>-18.88877435178952</v>
       </c>
       <c r="F80">
-        <v>-3.94180428405727</v>
+        <v>-3.84063319091421</v>
       </c>
       <c r="G80">
-        <v>-5.647867983212382</v>
+        <v>-6.497218236222259</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.97222281481133</v>
       </c>
       <c r="E81">
-        <v>-19.63361322809714</v>
+        <v>-19.82754512747562</v>
       </c>
       <c r="F81">
-        <v>-4.520829338624749</v>
+        <v>-3.473930045458995</v>
       </c>
       <c r="G81">
-        <v>-6.458997987971373</v>
+        <v>-6.732465602242869</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.019110930213373</v>
       </c>
       <c r="E82">
-        <v>-20.77688536149562</v>
+        <v>-20.50741851566919</v>
       </c>
       <c r="F82">
-        <v>-4.392675855947388</v>
+        <v>-3.708689108128246</v>
       </c>
       <c r="G82">
-        <v>-6.170917625689533</v>
+        <v>-5.508656232740489</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.030406922667277</v>
       </c>
       <c r="E83">
-        <v>-21.11930592358561</v>
+        <v>-20.97066782123185</v>
       </c>
       <c r="F83">
-        <v>-4.228445552516318</v>
+        <v>-3.163675721800745</v>
       </c>
       <c r="G83">
-        <v>-5.649874173809181</v>
+        <v>-6.058544467904512</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.994650827292117</v>
       </c>
       <c r="E84">
-        <v>-22.20922810469973</v>
+        <v>-21.23551562357045</v>
       </c>
       <c r="F84">
-        <v>-4.225905288227953</v>
+        <v>-3.972807702910871</v>
       </c>
       <c r="G84">
-        <v>-5.608535391660301</v>
+        <v>-4.984295614229787</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.898635607654271</v>
       </c>
       <c r="E85">
-        <v>-23.97858441202867</v>
+        <v>-23.79665749724452</v>
       </c>
       <c r="F85">
-        <v>-4.252037227685661</v>
+        <v>-3.573261664181272</v>
       </c>
       <c r="G85">
-        <v>-5.245947891471625</v>
+        <v>-5.089905327478077</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.730682894479804</v>
       </c>
       <c r="E86">
-        <v>-22.84301068444323</v>
+        <v>-24.89416487232149</v>
       </c>
       <c r="F86">
-        <v>-4.43285685058096</v>
+        <v>-3.659332913273575</v>
       </c>
       <c r="G86">
-        <v>-5.975731171239643</v>
+        <v>-6.085859779149039</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.482238136016914</v>
       </c>
       <c r="E87">
-        <v>-25.40447860824586</v>
+        <v>-26.08101451109578</v>
       </c>
       <c r="F87">
-        <v>-4.48236270564464</v>
+        <v>-3.641695180493326</v>
       </c>
       <c r="G87">
-        <v>-5.450943492354375</v>
+        <v>-4.375300899007616</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.147378901318923</v>
       </c>
       <c r="E88">
-        <v>-26.0454252338695</v>
+        <v>-26.84346915129323</v>
       </c>
       <c r="F88">
-        <v>-4.475565439855574</v>
+        <v>-3.547463094818764</v>
       </c>
       <c r="G88">
-        <v>-5.571765162355616</v>
+        <v>-4.91155961818646</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.723235842846298</v>
       </c>
       <c r="E89">
-        <v>-27.74643781147469</v>
+        <v>-28.23377859875815</v>
       </c>
       <c r="F89">
-        <v>-4.252696841199442</v>
+        <v>-3.471583785145271</v>
       </c>
       <c r="G89">
-        <v>-4.935352508977202</v>
+        <v>-4.865705251922014</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.209721893123382</v>
       </c>
       <c r="E90">
-        <v>-29.07827560255256</v>
+        <v>-28.15711153380829</v>
       </c>
       <c r="F90">
-        <v>-4.41073643820706</v>
+        <v>-3.658705765731061</v>
       </c>
       <c r="G90">
-        <v>-5.564101249432204</v>
+        <v>-6.114638351521923</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.6137495394322799</v>
       </c>
       <c r="E91">
-        <v>-30.40091606292086</v>
+        <v>-30.51050739814348</v>
       </c>
       <c r="F91">
-        <v>-4.8665800548187</v>
+        <v>-4.11823070674314</v>
       </c>
       <c r="G91">
-        <v>-5.065331147940067</v>
+        <v>-5.750249914559883</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.05694292149454271</v>
       </c>
       <c r="E92">
-        <v>-30.64492835635017</v>
+        <v>-32.28078298569599</v>
       </c>
       <c r="F92">
-        <v>-4.314227775279053</v>
+        <v>-4.138179066454016</v>
       </c>
       <c r="G92">
-        <v>-5.869035599054472</v>
+        <v>-5.022174876290128</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.791240104869026</v>
       </c>
       <c r="E93">
-        <v>-33.41191654451691</v>
+        <v>-32.65567044218398</v>
       </c>
       <c r="F93">
-        <v>-4.687519929195454</v>
+        <v>-4.093844803057204</v>
       </c>
       <c r="G93">
-        <v>-5.923636426633673</v>
+        <v>-6.26977713658325</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.568851681803412</v>
       </c>
       <c r="E94">
-        <v>-34.25166091484027</v>
+        <v>-35.40387678440391</v>
       </c>
       <c r="F94">
-        <v>-4.636404237068731</v>
+        <v>-4.202216215144809</v>
       </c>
       <c r="G94">
-        <v>-6.276060552016786</v>
+        <v>-5.413146993932516</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.373929050290323</v>
       </c>
       <c r="E95">
-        <v>-36.5668749505798</v>
+        <v>-37.25909295891828</v>
       </c>
       <c r="F95">
-        <v>-4.46102701955184</v>
+        <v>-4.21703020027783</v>
       </c>
       <c r="G95">
-        <v>-6.203533120342433</v>
+        <v>-5.966494749185077</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.18869045467793</v>
       </c>
       <c r="E96">
-        <v>-38.68048358773484</v>
+        <v>-39.68250808836008</v>
       </c>
       <c r="F96">
-        <v>-4.912910579521923</v>
+        <v>-3.54124150612996</v>
       </c>
       <c r="G96">
-        <v>-6.38587796864549</v>
+        <v>-5.80549960906478</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.986214319020339</v>
       </c>
       <c r="E97">
-        <v>-40.56545636495362</v>
+        <v>-40.31556837649936</v>
       </c>
       <c r="F97">
-        <v>-4.794267250866777</v>
+        <v>-4.174202833059559</v>
       </c>
       <c r="G97">
-        <v>-6.477023908432704</v>
+        <v>-7.905189943528756</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.75442435441366</v>
       </c>
       <c r="E98">
-        <v>-41.49915524975113</v>
+        <v>-41.93669867260924</v>
       </c>
       <c r="F98">
-        <v>-4.989600746624121</v>
+        <v>-3.98900426330807</v>
       </c>
       <c r="G98">
-        <v>-5.981160465924049</v>
+        <v>-5.228882029216682</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.46432186769187</v>
       </c>
       <c r="E99">
-        <v>-44.65914252619953</v>
+        <v>-43.54900297287817</v>
       </c>
       <c r="F99">
-        <v>-5.2511656156181</v>
+        <v>-4.386151779428736</v>
       </c>
       <c r="G99">
-        <v>-7.521070655152659</v>
+        <v>-8.086998483454451</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.108648265448657</v>
       </c>
       <c r="E100">
-        <v>-45.96348342310283</v>
+        <v>-46.68974876326799</v>
       </c>
       <c r="F100">
-        <v>-5.110064545229065</v>
+        <v>-4.22438888981392</v>
       </c>
       <c r="G100">
-        <v>-7.337663121731496</v>
+        <v>-8.882085584530133</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.651773774184342</v>
       </c>
       <c r="E101">
-        <v>-47.55962786387539</v>
+        <v>-48.9518822909266</v>
       </c>
       <c r="F101">
-        <v>-4.875579463683184</v>
+        <v>-3.8606805322448</v>
       </c>
       <c r="G101">
-        <v>-7.976300461712301</v>
+        <v>-7.819469987880407</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.112991001207199</v>
       </c>
       <c r="E102">
-        <v>-49.89246898468977</v>
+        <v>-49.60885178970788</v>
       </c>
       <c r="F102">
-        <v>-5.100286744907142</v>
+        <v>-4.593158771488784</v>
       </c>
       <c r="G102">
-        <v>-8.209253619674197</v>
+        <v>-7.34527406592628</v>
       </c>
     </row>
   </sheetData>
